--- a/docs/design/ACSMS-SCR-010/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_メニュー画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-010/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_メニュー画面_V1.0.xlsx
@@ -1700,7 +1700,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2171,7 +2171,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2815,7 +2815,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3250,7 +3250,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5484,7 +5484,7 @@
     <row r="67" ht="18" customHeight="1">
       <c r="C67" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7381,7 +7381,7 @@
     <row r="53" ht="18" customHeight="1">
       <c r="C53" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>

--- a/docs/design/ACSMS-SCR-010/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_メニュー画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-010/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_メニュー画面_V1.0.xlsx
@@ -1700,7 +1700,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2010,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -2171,7 +2171,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2546,71 +2546,15 @@
       <c r="AJ10" s="10" t="n"/>
       <c r="AK10" s="11" t="n"/>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>画面固有</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="19" t="inlineStr">
-        <is>
-          <t>DENSHI_NOT_ENABLED</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="10" t="n"/>
-      <c r="M11" s="10" t="n"/>
-      <c r="N11" s="10" t="n"/>
-      <c r="O11" s="10" t="n"/>
-      <c r="P11" s="10" t="n"/>
-      <c r="Q11" s="10" t="n"/>
-      <c r="R11" s="10" t="n"/>
-      <c r="S11" s="10" t="n"/>
-      <c r="T11" s="10" t="n"/>
-      <c r="U11" s="11" t="n"/>
-      <c r="V11" s="19" t="inlineStr">
-        <is>
-          <t>このアカウントでは電子版機能が有効化されていません。</t>
-        </is>
-      </c>
-      <c r="W11" s="10" t="n"/>
-      <c r="X11" s="10" t="n"/>
-      <c r="Y11" s="10" t="n"/>
-      <c r="Z11" s="10" t="n"/>
-      <c r="AA11" s="10" t="n"/>
-      <c r="AB11" s="10" t="n"/>
-      <c r="AC11" s="10" t="n"/>
-      <c r="AD11" s="10" t="n"/>
-      <c r="AE11" s="10" t="n"/>
-      <c r="AF11" s="10" t="n"/>
-      <c r="AG11" s="10" t="n"/>
-      <c r="AH11" s="10" t="n"/>
-      <c r="AI11" s="10" t="n"/>
-      <c r="AJ11" s="10" t="n"/>
-      <c r="AK11" s="11" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="V11:AK11"/>
+  <mergeCells count="38">
     <mergeCell ref="J6:U6"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A11:B11"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="V7:AK7"/>
-    <mergeCell ref="J11:U11"/>
     <mergeCell ref="J7:U7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="Q2:U3"/>
@@ -2641,7 +2585,6 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="V6:AK6"/>
-    <mergeCell ref="C11:I11"/>
     <mergeCell ref="J9:U9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2815,7 +2758,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3017,7 +2960,7 @@
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="19" t="inlineStr">
         <is>
-          <t>電子版読者の承認待ち件数を取得する（電子版取扱アカウントのみ）</t>
+          <t>電子版読者の承認待ち件数を取得する（`dokusya.view` 権限保持者。denshi_flg によるアクセス制限は無い）</t>
         </is>
       </c>
       <c r="T7" s="10" t="n"/>
@@ -3089,7 +3032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK93"/>
+  <dimension ref="A1:AK92"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3250,7 +3193,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3895,7 +3838,7 @@
       <c r="AE21" s="11" t="n"/>
       <c r="AF21" s="19" t="inlineStr">
         <is>
-          <t>お知らせ一覧の最大取得件数（デフォルト: 20、最大: 100）</t>
+          <t>お知らせ一覧の最大取得件数（デフォルト: 20、最大: 20）</t>
         </is>
       </c>
       <c r="AG21" s="10" t="n"/>
@@ -4341,12 +4284,12 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" s="38" t="n"/>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>oshirase_type_label</t>
+          <t>publish_start_date</t>
         </is>
       </c>
       <c r="E32" s="10" t="n"/>
@@ -4372,7 +4315,11 @@
       </c>
       <c r="R32" s="10" t="n"/>
       <c r="S32" s="11" t="n"/>
-      <c r="T32" s="17" t="inlineStr"/>
+      <c r="T32" s="17" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD HH:mm</t>
+        </is>
+      </c>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
       <c r="W32" s="10" t="n"/>
@@ -4390,7 +4337,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>お知らせ種別ラベル</t>
+          <t>公開開始日時</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -4401,12 +4348,12 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33" s="38" t="n"/>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>publish_start_date</t>
+          <t>publish_end_date</t>
         </is>
       </c>
       <c r="E33" s="10" t="n"/>
@@ -4443,7 +4390,7 @@
       <c r="X33" s="11" t="n"/>
       <c r="Y33" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z33" s="10" t="n"/>
@@ -4454,7 +4401,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>公開開始日時</t>
+          <t>公開終了日時（NULL = 無期限）</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -4463,14 +4410,14 @@
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="54" customHeight="1">
       <c r="B34" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="38" t="n"/>
       <c r="D34" s="19" t="inlineStr">
         <is>
-          <t>publish_end_date</t>
+          <t>is_new</t>
         </is>
       </c>
       <c r="E34" s="10" t="n"/>
@@ -4483,7 +4430,7 @@
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N34" s="10" t="n"/>
@@ -4496,18 +4443,14 @@
       </c>
       <c r="R34" s="10" t="n"/>
       <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD HH:mm</t>
-        </is>
-      </c>
+      <c r="T34" s="17" t="inlineStr"/>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n"/>
       <c r="Y34" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z34" s="10" t="n"/>
@@ -4518,7 +4461,7 @@
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>公開終了日時（NULL = 無期限）</t>
+          <t>NEWフラグ（更新日時から7日以内の場合 true。updated_at が NULL の場合は created_at で判定）</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -4529,12 +4472,12 @@
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>is_new</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E35" s="10" t="n"/>
@@ -4547,7 +4490,7 @@
       <c r="L35" s="11" t="n"/>
       <c r="M35" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N35" s="10" t="n"/>
@@ -4567,7 +4510,7 @@
       <c r="X35" s="11" t="n"/>
       <c r="Y35" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z35" s="10" t="n"/>
@@ -4578,7 +4521,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>NEWフラグ（公開開始日から7日以内の場合 true）</t>
+          <t>JA ID（NULL=全JA向け）</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -4589,12 +4532,12 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>deadline_notice</t>
         </is>
       </c>
       <c r="E36" s="10" t="n"/>
@@ -4607,7 +4550,7 @@
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
@@ -4638,7 +4581,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>JA ID（NULL=全JA向け）</t>
+          <t>締め切り時間お知らせ（該当なしの場合 null）</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4649,12 +4592,12 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>deadline_notice</t>
+          <t>oshirase_id</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -4667,7 +4610,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -4687,7 +4630,7 @@
       <c r="X37" s="11" t="n"/>
       <c r="Y37" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z37" s="10" t="n"/>
@@ -4698,7 +4641,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>締め切り時間お知らせ（該当なしの場合 null）</t>
+          <t>お知らせID</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4709,12 +4652,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>oshirase_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4727,7 +4670,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -4758,7 +4701,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>お知らせID</t>
+          <t>お知らせタイトル</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4769,12 +4712,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>content</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4818,7 +4761,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>お知らせタイトル</t>
+          <t>内容</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -4829,12 +4772,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>oshirase_type</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -4847,7 +4790,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -4878,7 +4821,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>お知らせ種別（4:締め切り時間 固定）</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -4889,12 +4832,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>oshirase_type</t>
+          <t>publish_start_date</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -4907,7 +4850,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -4920,7 +4863,11 @@
       </c>
       <c r="R41" s="10" t="n"/>
       <c r="S41" s="11" t="n"/>
-      <c r="T41" s="17" t="inlineStr"/>
+      <c r="T41" s="17" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD HH:mm</t>
+        </is>
+      </c>
       <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="n"/>
       <c r="W41" s="10" t="n"/>
@@ -4938,7 +4885,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>お知らせ種別（4:締め切り時間 固定）</t>
+          <t>公開開始日時</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -4949,12 +4896,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>oshirase_type_label</t>
+          <t>publish_end_date</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -4980,14 +4927,18 @@
       </c>
       <c r="R42" s="10" t="n"/>
       <c r="S42" s="11" t="n"/>
-      <c r="T42" s="17" t="inlineStr"/>
+      <c r="T42" s="17" t="inlineStr">
+        <is>
+          <t>YYYY/MM/DD HH:mm</t>
+        </is>
+      </c>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n"/>
       <c r="Y42" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z42" s="10" t="n"/>
@@ -4998,7 +4949,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>お知らせ種別ラベル（締め切り時間）</t>
+          <t>公開終了日時（NULL = 無期限）</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5007,14 +4958,14 @@
       <c r="AJ42" s="10" t="n"/>
       <c r="AK42" s="11" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1">
+    <row r="43" ht="54" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C43" s="38" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="C43" s="39" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>publish_start_date</t>
+          <t>is_new</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5027,7 +4978,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -5040,11 +4991,7 @@
       </c>
       <c r="R43" s="10" t="n"/>
       <c r="S43" s="11" t="n"/>
-      <c r="T43" s="17" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD HH:mm</t>
-        </is>
-      </c>
+      <c r="T43" s="17" t="inlineStr"/>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
       <c r="W43" s="10" t="n"/>
@@ -5062,7 +5009,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>公開開始日時</t>
+          <t>NEWフラグ（更新日時から7日以内の場合 true。updated_at が NULL の場合は created_at で判定）</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5071,188 +5018,64 @@
       <c r="AJ43" s="10" t="n"/>
       <c r="AK43" s="11" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="31" t="n">
-        <v>19</v>
-      </c>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="19" t="inlineStr">
-        <is>
-          <t>publish_end_date</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="10" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="11" t="n"/>
-      <c r="M44" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N44" s="10" t="n"/>
-      <c r="O44" s="10" t="n"/>
-      <c r="P44" s="11" t="n"/>
-      <c r="Q44" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R44" s="10" t="n"/>
-      <c r="S44" s="11" t="n"/>
-      <c r="T44" s="17" t="inlineStr">
-        <is>
-          <t>YYYY/MM/DD HH:mm</t>
-        </is>
-      </c>
-      <c r="U44" s="10" t="n"/>
-      <c r="V44" s="10" t="n"/>
-      <c r="W44" s="10" t="n"/>
-      <c r="X44" s="11" t="n"/>
-      <c r="Y44" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Z44" s="10" t="n"/>
-      <c r="AA44" s="10" t="n"/>
-      <c r="AB44" s="10" t="n"/>
-      <c r="AC44" s="10" t="n"/>
-      <c r="AD44" s="10" t="n"/>
-      <c r="AE44" s="11" t="n"/>
-      <c r="AF44" s="19" t="inlineStr">
-        <is>
-          <t>公開終了日時（NULL = 無期限）</t>
-        </is>
-      </c>
-      <c r="AG44" s="10" t="n"/>
-      <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="10" t="n"/>
-      <c r="AJ44" s="10" t="n"/>
-      <c r="AK44" s="11" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C45" s="39" t="n"/>
-      <c r="D45" s="19" t="inlineStr">
-        <is>
-          <t>is_new</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
-      <c r="J45" s="10" t="n"/>
-      <c r="K45" s="10" t="n"/>
-      <c r="L45" s="11" t="n"/>
-      <c r="M45" s="17" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="N45" s="10" t="n"/>
-      <c r="O45" s="10" t="n"/>
-      <c r="P45" s="11" t="n"/>
-      <c r="Q45" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R45" s="10" t="n"/>
-      <c r="S45" s="11" t="n"/>
-      <c r="T45" s="17" t="inlineStr"/>
-      <c r="U45" s="10" t="n"/>
-      <c r="V45" s="10" t="n"/>
-      <c r="W45" s="10" t="n"/>
-      <c r="X45" s="11" t="n"/>
-      <c r="Y45" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z45" s="10" t="n"/>
-      <c r="AA45" s="10" t="n"/>
-      <c r="AB45" s="10" t="n"/>
-      <c r="AC45" s="10" t="n"/>
-      <c r="AD45" s="10" t="n"/>
-      <c r="AE45" s="11" t="n"/>
-      <c r="AF45" s="19" t="inlineStr">
-        <is>
-          <t>NEWフラグ（公開開始日から7日以内の場合 true）</t>
-        </is>
-      </c>
-      <c r="AG45" s="10" t="n"/>
-      <c r="AH45" s="10" t="n"/>
-      <c r="AI45" s="10" t="n"/>
-      <c r="AJ45" s="10" t="n"/>
-      <c r="AK45" s="11" t="n"/>
-    </row>
-    <row r="46" ht="19.5" customHeight="1"/>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="B47" s="40" t="inlineStr">
+    <row r="44" ht="19.5" customHeight="1"/>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="C48" s="19" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/oshirase/menu?limit=20</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="10" t="n"/>
-      <c r="H48" s="10" t="n"/>
-      <c r="I48" s="10" t="n"/>
-      <c r="J48" s="10" t="n"/>
-      <c r="K48" s="10" t="n"/>
-      <c r="L48" s="10" t="n"/>
-      <c r="M48" s="10" t="n"/>
-      <c r="N48" s="10" t="n"/>
-      <c r="O48" s="10" t="n"/>
-      <c r="P48" s="10" t="n"/>
-      <c r="Q48" s="10" t="n"/>
-      <c r="R48" s="10" t="n"/>
-      <c r="S48" s="10" t="n"/>
-      <c r="T48" s="10" t="n"/>
-      <c r="U48" s="10" t="n"/>
-      <c r="V48" s="10" t="n"/>
-      <c r="W48" s="10" t="n"/>
-      <c r="X48" s="10" t="n"/>
-      <c r="Y48" s="10" t="n"/>
-      <c r="Z48" s="10" t="n"/>
-      <c r="AA48" s="10" t="n"/>
-      <c r="AB48" s="10" t="n"/>
-      <c r="AC48" s="10" t="n"/>
-      <c r="AD48" s="10" t="n"/>
-      <c r="AE48" s="10" t="n"/>
-      <c r="AF48" s="10" t="n"/>
-      <c r="AG48" s="10" t="n"/>
-      <c r="AH48" s="10" t="n"/>
-      <c r="AI48" s="10" t="n"/>
-      <c r="AJ48" s="10" t="n"/>
-      <c r="AK48" s="11" t="n"/>
-    </row>
-    <row r="50" ht="19.5" customHeight="1">
-      <c r="B50" s="40" t="inlineStr">
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="10" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="10" t="n"/>
+      <c r="AC46" s="10" t="n"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="10" t="n"/>
+      <c r="AF46" s="10" t="n"/>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="11" t="n"/>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="409" customHeight="1">
-      <c r="C51" s="19" t="inlineStr">
+    <row r="49" ht="409" customHeight="1">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -5262,7 +5085,6 @@
         "title": "システムメンテナンスのお知らせ",
         "content": "4月20日（月）02:00〜06:00にシステムメンテナンスを実施いたします。",
         "oshirase_type": 1,
-        "oshirase_type_label": "システム",
         "publish_start_date": "2026/04/10 10:00",
         "publish_end_date": "2026/04/20 06:00",
         "is_new": true,
@@ -5273,7 +5095,6 @@
         "title": "新機能リリースのお知らせ",
         "content": "新機能がリリースされました。",
         "oshirase_type": 3,
-        "oshirase_type_label": "一般",
         "publish_start_date": "2026/04/01 09:00",
         "publish_end_date": null,
         "is_new": false,
@@ -5285,7 +5106,6 @@
       "title": "【重要】締め切り時間の変更について",
       "content": "2026年4月より締め切り時間を17:00に変更いたします。",
       "oshirase_type": 4,
-      "oshirase_type_label": "締め切り時間",
       "publish_start_date": "2026/04/15 09:00",
       "publish_end_date": null,
       "is_new": true
@@ -5294,50 +5114,50 @@
 }</t>
         </is>
       </c>
-      <c r="D51" s="10" t="n"/>
-      <c r="E51" s="10" t="n"/>
-      <c r="F51" s="10" t="n"/>
-      <c r="G51" s="10" t="n"/>
-      <c r="H51" s="10" t="n"/>
-      <c r="I51" s="10" t="n"/>
-      <c r="J51" s="10" t="n"/>
-      <c r="K51" s="10" t="n"/>
-      <c r="L51" s="10" t="n"/>
-      <c r="M51" s="10" t="n"/>
-      <c r="N51" s="10" t="n"/>
-      <c r="O51" s="10" t="n"/>
-      <c r="P51" s="10" t="n"/>
-      <c r="Q51" s="10" t="n"/>
-      <c r="R51" s="10" t="n"/>
-      <c r="S51" s="10" t="n"/>
-      <c r="T51" s="10" t="n"/>
-      <c r="U51" s="10" t="n"/>
-      <c r="V51" s="10" t="n"/>
-      <c r="W51" s="10" t="n"/>
-      <c r="X51" s="10" t="n"/>
-      <c r="Y51" s="10" t="n"/>
-      <c r="Z51" s="10" t="n"/>
-      <c r="AA51" s="10" t="n"/>
-      <c r="AB51" s="10" t="n"/>
-      <c r="AC51" s="10" t="n"/>
-      <c r="AD51" s="10" t="n"/>
-      <c r="AE51" s="10" t="n"/>
-      <c r="AF51" s="10" t="n"/>
-      <c r="AG51" s="10" t="n"/>
-      <c r="AH51" s="10" t="n"/>
-      <c r="AI51" s="10" t="n"/>
-      <c r="AJ51" s="10" t="n"/>
-      <c r="AK51" s="11" t="n"/>
-    </row>
-    <row r="53" ht="19.5" customHeight="1">
-      <c r="B53" s="40" t="inlineStr">
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="10" t="n"/>
+      <c r="K49" s="10" t="n"/>
+      <c r="L49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n"/>
+      <c r="W49" s="10" t="n"/>
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="10" t="n"/>
+      <c r="Z49" s="10" t="n"/>
+      <c r="AA49" s="10" t="n"/>
+      <c r="AB49" s="10" t="n"/>
+      <c r="AC49" s="10" t="n"/>
+      <c r="AD49" s="10" t="n"/>
+      <c r="AE49" s="10" t="n"/>
+      <c r="AF49" s="10" t="n"/>
+      <c r="AG49" s="10" t="n"/>
+      <c r="AH49" s="10" t="n"/>
+      <c r="AI49" s="10" t="n"/>
+      <c r="AJ49" s="10" t="n"/>
+      <c r="AK49" s="11" t="n"/>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="72" customHeight="1">
-      <c r="C54" s="19" t="inlineStr">
+    <row r="52" ht="72" customHeight="1">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -5345,50 +5165,50 @@
 }</t>
         </is>
       </c>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
-      <c r="I54" s="10" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="10" t="n"/>
-      <c r="L54" s="10" t="n"/>
-      <c r="M54" s="10" t="n"/>
-      <c r="N54" s="10" t="n"/>
-      <c r="O54" s="10" t="n"/>
-      <c r="P54" s="10" t="n"/>
-      <c r="Q54" s="10" t="n"/>
-      <c r="R54" s="10" t="n"/>
-      <c r="S54" s="10" t="n"/>
-      <c r="T54" s="10" t="n"/>
-      <c r="U54" s="10" t="n"/>
-      <c r="V54" s="10" t="n"/>
-      <c r="W54" s="10" t="n"/>
-      <c r="X54" s="10" t="n"/>
-      <c r="Y54" s="10" t="n"/>
-      <c r="Z54" s="10" t="n"/>
-      <c r="AA54" s="10" t="n"/>
-      <c r="AB54" s="10" t="n"/>
-      <c r="AC54" s="10" t="n"/>
-      <c r="AD54" s="10" t="n"/>
-      <c r="AE54" s="10" t="n"/>
-      <c r="AF54" s="10" t="n"/>
-      <c r="AG54" s="10" t="n"/>
-      <c r="AH54" s="10" t="n"/>
-      <c r="AI54" s="10" t="n"/>
-      <c r="AJ54" s="10" t="n"/>
-      <c r="AK54" s="11" t="n"/>
-    </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="B56" s="40" t="inlineStr">
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="10" t="n"/>
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="10" t="n"/>
+      <c r="AF52" s="10" t="n"/>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="72" customHeight="1">
-      <c r="C57" s="19" t="inlineStr">
+    <row r="55" ht="72" customHeight="1">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -5396,398 +5216,406 @@
 }</t>
         </is>
       </c>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="10" t="n"/>
-      <c r="L57" s="10" t="n"/>
-      <c r="M57" s="10" t="n"/>
-      <c r="N57" s="10" t="n"/>
-      <c r="O57" s="10" t="n"/>
-      <c r="P57" s="10" t="n"/>
-      <c r="Q57" s="10" t="n"/>
-      <c r="R57" s="10" t="n"/>
-      <c r="S57" s="10" t="n"/>
-      <c r="T57" s="10" t="n"/>
-      <c r="U57" s="10" t="n"/>
-      <c r="V57" s="10" t="n"/>
-      <c r="W57" s="10" t="n"/>
-      <c r="X57" s="10" t="n"/>
-      <c r="Y57" s="10" t="n"/>
-      <c r="Z57" s="10" t="n"/>
-      <c r="AA57" s="10" t="n"/>
-      <c r="AB57" s="10" t="n"/>
-      <c r="AC57" s="10" t="n"/>
-      <c r="AD57" s="10" t="n"/>
-      <c r="AE57" s="10" t="n"/>
-      <c r="AF57" s="10" t="n"/>
-      <c r="AG57" s="10" t="n"/>
-      <c r="AH57" s="10" t="n"/>
-      <c r="AI57" s="10" t="n"/>
-      <c r="AJ57" s="10" t="n"/>
-      <c r="AK57" s="11" t="n"/>
-    </row>
-    <row r="59" ht="19.5" customHeight="1"/>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1"/>
+    <row r="58" ht="19.5" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="B61" s="27" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="C60" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータの検証：</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="D61" s="41" t="inlineStr">
+        <is>
+          <t>limit：数値型チェック、1〜20（範囲外・数値変換不可な値は 1〜20 にクランプ、またはデフォルト値にフォールバック。エラーは返却しない）</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="C62" s="41" t="inlineStr">
         <is>
-          <t>クエリパラメータの検証：</t>
+          <t>デフォルト値を設定する（limit=20）</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="D63" s="41" t="inlineStr">
-        <is>
-          <t>limit：数値型チェック、1〜100</t>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="C64" s="41" t="inlineStr">
         <is>
-          <t>デフォルト値を設定する（limit=20）</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="C65" s="41" t="inlineStr">
         <is>
-          <t>不正なパラメータの場合：HTTP 400 (`BAD_REQUEST`)</t>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="B66" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C66" s="41" t="inlineStr">
+        <is>
+          <t>本APIは認証済みユーザーであれば誰でもアクセス可能（特定の permission は不要）。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1">
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
       <c r="C68" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>ログインユーザーの ja_id・role_id を取得する（日農アカウントは ja_id=NULL）。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="C69" s="41" t="inlineStr">
         <is>
-          <t>本APIは認証済みユーザーであれば誰でもアクセス可能（特定の permission は不要）。</t>
+          <t>共通条件：</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>`publish_location IN (2, 3)`（メニュー画面向け＝通常2／締め切り時間3）</t>
         </is>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーの ja_id を取得する（日農アカウントは NULL）。</t>
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>`status = 2`（公開中）</t>
         </is>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="C72" s="41" t="inlineStr">
-        <is>
-          <t>共通条件：</t>
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>`deleted_at IS NULL`</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="D73" s="41" t="inlineStr">
         <is>
-          <t>`publish_location = 2`（メニュー画面向け）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
+          <t>`publish_start_date &lt;= NOW()`（公開開始済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="36" customHeight="1">
       <c r="D74" s="41" t="inlineStr">
         <is>
-          <t>`status = 2`（公開中）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
+          <t>`publish_end_date IS NULL OR publish_end_date &gt;= NOW()`（未終了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="36" customHeight="1">
       <c r="D75" s="41" t="inlineStr">
         <is>
-          <t>`deleted_at IS NULL`</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
+          <t>`ja_id IS NULL OR ja_id = :user_ja_id`（全JA向け、またはユーザーのJA向け。日農=ja_id NULL は `ja_id IS NULL` のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="72" customHeight="1">
       <c r="D76" s="41" t="inlineStr">
         <is>
-          <t>`publish_start_date &lt;= NOW()`（公開開始済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="36" customHeight="1">
-      <c r="D77" s="41" t="inlineStr">
-        <is>
-          <t>`publish_end_date IS NULL OR publish_end_date &gt;= NOW()`（未終了）</t>
+          <t>対象管理者区分：`target_kanri_kubun = '' OR (',' || target_kanri_kubun || ',') LIKE '%,' || :role_id || ',%'`（未設定=全ロール向け、または閲覧者の role_id を含む）。カンマ括り方式でトークン単位一致（role 3 が "13" に誤マッチしない）。全ロール（日農含む）に一律適用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="C77" s="41" t="inlineStr">
+        <is>
+          <t>oshirase_list 追加条件：`oshirase_type != 4`（締め切り時間を除外）</t>
         </is>
       </c>
     </row>
     <row r="78" ht="36" customHeight="1">
-      <c r="D78" s="41" t="inlineStr">
-        <is>
-          <t>`ja_id IS NULL OR ja_id = :user_ja_id`（全JA向け、またはユーザーのJA向け）</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>deadline_notice 追加条件：`oshirase_type = 4`（締め切り時間のみ、1件のみ取得）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
       <c r="C79" s="41" t="inlineStr">
         <is>
-          <t>oshirase_list 追加条件：`oshirase_type != 4`（締め切り時間を除外）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>deadline_notice 追加条件：`oshirase_type = 4`（締め切り時間のみ、1件のみ取得）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
+          <t>並び順：`COALESCE(updated_at, created_at) DESC`（更新日時の新しい順。updated_at が無ければ created_at）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>4.4 通常お知らせ一覧の取得（oshirase_list）</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="234" customHeight="1">
-      <c r="C82" s="42" t="inlineStr">
+    <row r="81" ht="252" customHeight="1">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t>SELECT oshirase_id, ja_id, oshirase_type,
        title, content, publish_start_date, publish_end_date,
-       created_at
+       created_at, updated_at
 FROM t_oshirase
-WHERE publish_location = 2
+WHERE publish_location IN (2, 3)
   AND status = 2
   AND oshirase_type != 4
   AND deleted_at IS NULL
   AND publish_start_date &lt;= NOW()
   AND (publish_end_date IS NULL OR publish_end_date &gt;= NOW())
   AND (ja_id IS NULL OR ja_id = :user_ja_id)
-ORDER BY publish_start_date DESC
+  AND (target_kanri_kubun = '' OR (',' || target_kanri_kubun || ',') LIKE '%,' || :role_id || ',%')
+ORDER BY COALESCE(updated_at, created_at) DESC
 LIMIT :limit</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n"/>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="10" t="n"/>
-      <c r="T82" s="10" t="n"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="10" t="n"/>
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="10" t="n"/>
-      <c r="AF82" s="10" t="n"/>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="B83" s="27" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>4.5 締め切り時間の取得（deadline_notice）</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>`publish_location = 2` かつ `oshirase_type = 4` のお知らせは業務ルールで最大1件のみ登録される（ACSMS-SCR-031 の登録チェック参照）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="216" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
+    <row r="83" ht="36" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>`publish_location = 3` かつ `oshirase_type = 4` のお知らせは業務ルールで最大1件のみ登録される（ACSMS-SCR-031 の登録チェック参照）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="252" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
         <is>
           <t>SELECT oshirase_id, oshirase_type,
        title, content, publish_start_date, publish_end_date,
-       created_at
+       created_at, updated_at
 FROM t_oshirase
-WHERE publish_location = 2
+WHERE publish_location IN (2, 3)
   AND oshirase_type = 4
   AND status = 2
   AND deleted_at IS NULL
   AND publish_start_date &lt;= NOW()
   AND (publish_end_date IS NULL OR publish_end_date &gt;= NOW())
-ORDER BY publish_start_date DESC
+  AND (ja_id IS NULL OR ja_id = :user_ja_id)
+  AND (target_kanri_kubun = '' OR (',' || target_kanri_kubun || ',') LIKE '%,' || :role_id || ',%')
+ORDER BY COALESCE(updated_at, created_at) DESC
 LIMIT 1</t>
         </is>
       </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>該当レコードが存在しない場合は `deadline_notice` に `null` を設定する。</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>該当レコードが存在しない場合は `deadline_notice` に `null` を設定する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="B87" s="27" t="inlineStr">
+      <c r="B86" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="54" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>oshirase_type は数値のままレスポンスに含める（ラベル文字列への変換は行わない。認証済みエンドポイントは `*_label` を返却しない方針 — ラベルは FE が m_code キャッシュから解決する）。</t>
         </is>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="C88" s="41" t="inlineStr">
         <is>
-          <t>oshirase_type 値をラベルにマッピング（1→システム, 2→重要, 3→一般, 4→締め切り時間）</t>
+          <t>publish_start_date / publish_end_date を `YYYY/MM/DD HH:mm` 形式でフォーマットする。</t>
         </is>
       </c>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>publish_start_date / publish_end_date を `YYYY/MM/DD HH:mm` 形式でフォーマットする。</t>
+          <t>is_new フラグ：`COALESCE(updated_at, created_at)`（更新日時。NULL の場合は作成日時）が現在日時から7日以内であれば true、それ以外は false</t>
         </is>
       </c>
     </row>
     <row r="90" ht="36" customHeight="1">
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>is_new フラグ：`publish_start_date` が現在日時から7日以内であれば true、それ以外は false</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="36" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
-        <is>
           <t>`data.oshirase_list`（配列）と `data.deadline_notice`（オブジェクト または null）を含む JSON を返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="B92" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
+      <c r="C92" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="221">
+  <mergeCells count="210">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y27:AE27"/>
-    <mergeCell ref="C57:AK57"/>
-    <mergeCell ref="D78:AK78"/>
     <mergeCell ref="Y36:AE36"/>
-    <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="T33:X33"/>
+    <mergeCell ref="D71:AK71"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
+    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="M29:P29"/>
-    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="C68:AK68"/>
     <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="B48:I48"/>
     <mergeCell ref="D73:AK73"/>
     <mergeCell ref="M43:P43"/>
-    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="C65:AK65"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="D33:L33"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
@@ -5796,47 +5624,47 @@
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Y21:AB21"/>
     <mergeCell ref="M35:P35"/>
-    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="C20:L20"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="D35:L35"/>
+    <mergeCell ref="C27:C43"/>
     <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="C51:AK51"/>
     <mergeCell ref="D34:L34"/>
     <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="D77:AK77"/>
     <mergeCell ref="Y26:AE26"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="C48:AK48"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="T37:X37"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="D61:AK61"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="D75:AK75"/>
-    <mergeCell ref="B66:AK66"/>
     <mergeCell ref="M33:P33"/>
-    <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
-    <mergeCell ref="B47:I47"/>
     <mergeCell ref="T20:X20"/>
+    <mergeCell ref="D72:AK72"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="T38:X38"/>
+    <mergeCell ref="C49:AK49"/>
+    <mergeCell ref="B86:AK86"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="AC20:AE20"/>
     <mergeCell ref="A23:AK23"/>
     <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="B67:AK67"/>
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B61:AK61"/>
-    <mergeCell ref="Q44:S44"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="C88:AK88"/>
     <mergeCell ref="AF32:AK32"/>
@@ -5845,14 +5673,12 @@
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="M44:P44"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="AC21:AE21"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D29:L29"/>
-    <mergeCell ref="D63:AK63"/>
+    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
@@ -5866,33 +5692,32 @@
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M21:P21"/>
     <mergeCell ref="Y31:AE31"/>
     <mergeCell ref="D76:AK76"/>
-    <mergeCell ref="B81:AK81"/>
-    <mergeCell ref="B50:I50"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M37:P37"/>
-    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="D27:L27"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T32:X32"/>
-    <mergeCell ref="T45:X45"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
-    <mergeCell ref="AF45:AK45"/>
     <mergeCell ref="C62:AK62"/>
     <mergeCell ref="Y41:AE41"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -5900,7 +5725,6 @@
     <mergeCell ref="D28:L28"/>
     <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="T44:X44"/>
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
@@ -5908,22 +5732,19 @@
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="C54:AK54"/>
+    <mergeCell ref="A58:AK58"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="T21:X21"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="T26:X26"/>
-    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="B14:I16"/>
-    <mergeCell ref="A60:AK60"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
-    <mergeCell ref="Y44:AE44"/>
+    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
@@ -5940,47 +5761,45 @@
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="A18:AK18"/>
-    <mergeCell ref="C67:AK67"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
+    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="T35:X35"/>
+    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="D74:AK74"/>
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="AF20:AK20"/>
     <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B53:I53"/>
-    <mergeCell ref="B83:AK83"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="M20:P20"/>
-    <mergeCell ref="D44:L44"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="Y20:AB20"/>
     <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="C27:C45"/>
+    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="C21:L21"/>
     <mergeCell ref="D31:L31"/>
     <mergeCell ref="Y34:AE34"/>
     <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="D70:AK70"/>
     <mergeCell ref="M28:P28"/>
+    <mergeCell ref="B59:AK59"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="AF29:AK29"/>
     <mergeCell ref="Q20:S20"/>
@@ -5995,7 +5814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK73"/>
+  <dimension ref="A1:AK69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6156,7 +5975,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6280,7 +6099,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>電子版読者の承認待ち件数を取得する（電子版取扱アカウントのみ）</t>
+          <t>電子版読者の承認待ち件数を取得する（`dokusya.view` 権限保持者。denshi_flg によるアクセス制限は無い）</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -6638,7 +6457,7 @@
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>電子版機能が有効化されていません / この画面へのアクセス権限がありません</t>
+          <t>この画面へのアクセス権限がありません</t>
         </is>
       </c>
       <c r="O16" s="10" t="n"/>
@@ -7199,7 +7018,7 @@
     <row r="39" ht="19.5" customHeight="1">
       <c r="B39" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden（電子版機能が無効））</t>
+          <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
@@ -7207,8 +7026,8 @@
       <c r="C40" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "DENSHI_NOT_ENABLED",
-  "message": "このアカウントでは電子版機能が有効化されていません"
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません"
 }</t>
         </is>
       </c>
@@ -7250,7 +7069,7 @@
     <row r="42" ht="19.5" customHeight="1">
       <c r="B42" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
@@ -7258,8 +7077,8 @@
       <c r="C43" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
 }</t>
         </is>
       </c>
@@ -7298,311 +7117,250 @@
       <c r="AJ43" s="10" t="n"/>
       <c r="AK43" s="11" t="n"/>
     </row>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="B45" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="72" customHeight="1">
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
-}</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="11" t="n"/>
-    </row>
-    <row r="48" ht="19.5" customHeight="1"/>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="27" t="inlineStr">
+    <row r="45" ht="19.5" customHeight="1"/>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="C48" s="41" t="inlineStr">
+        <is>
+          <t>リクエストパラメータなし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="B50" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>リクエストパラメータなし。</t>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C52" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`dokusya.view` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="C53" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="C54" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
       <c r="C55" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`dokusya.view` を保持しているか確認する。</t>
+          <t>ログインユーザーのスコープを取得する（ja_id, kanri_shiten_id, shiten_id, role_code）。</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
-      <c r="D56" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>DataScope（`applyBranchScope` + `applyShitenScope`）：</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="C58" s="41" t="inlineStr">
-        <is>
-          <t>電子版取扱フラグ確認：`m_account.denshi_flg = true` であること。</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
-        <is>
-          <t>`denshi_flg = false` の場合：HTTP 403 (`DENSHI_NOT_ENABLED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="36" customHeight="1">
+      <c r="D57" s="41" t="inlineStr">
+        <is>
+          <t>`CHUOKAI` / `JA_HONTEN`：`ja_id = :user_ja_id`</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="D58" s="41" t="inlineStr">
+        <is>
+          <t>`JA_KANRI_SHITEN`：`ja_id = :user_ja_id AND kanri_shiten_id = :user_kanri_shiten_id`</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="54" customHeight="1">
+      <c r="D59" s="41" t="inlineStr">
+        <is>
+          <t>`session.shiten_id` が設定されている場合（JA管理支店アカウントが特定の支店に紐づく場合。顧客要件2026-07）：さらに `shiten_id = :user_shiten_id` を追加する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="D60" s="41" t="inlineStr">
+        <is>
+          <t>`NICHINO_ADMIN` / `NICHINO_STAFF`（`ja_id IS NULL`）：スコープ条件を付けず全件対象（FE 側でバナー自体を非表示にする運用）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>ログインユーザーのスコープを取得する（ja_id, kanri_shiten_id, role_code）。</t>
+          <t>絞り込み条件：</t>
         </is>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="C62" s="41" t="inlineStr">
-        <is>
-          <t>DataScope：</t>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>`denshi_shonin_status = 0`（未承認/承認待ち）</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="D63" s="41" t="inlineStr">
         <is>
-          <t>`CHUOKAI` / `JA_HONTEN`：`ja_id = :user_ja_id`</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="36" customHeight="1">
-      <c r="D64" s="41" t="inlineStr">
-        <is>
-          <t>`JA_KANRI_SHITEN`：`ja_id = :user_ja_id AND kanri_shiten_id = :user_kanri_shiten_id`</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>絞り込み条件：</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="D66" s="41" t="inlineStr">
-        <is>
-          <t>`denshi_shonin_status = 1`（未承認/承認待ち）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="D67" s="41" t="inlineStr">
-        <is>
           <t>`deleted_at IS NULL`（削除されていない）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="B68" s="27" t="inlineStr">
+    <row r="64" ht="18" customHeight="1">
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="126" customHeight="1">
-      <c r="C69" s="42" t="inlineStr">
+    <row r="65" ht="126" customHeight="1">
+      <c r="C65" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS count
 FROM t_dokusya
-WHERE denshi_shonin_status = 1
+WHERE denshi_shonin_status = 0
   AND deleted_at IS NULL
   AND ja_id = :user_ja_id
   /* JA_KANRI_SHITEN の場合は以下を追加 */
   AND kanri_shiten_id = :user_kanri_shiten_id</t>
         </is>
       </c>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n"/>
-      <c r="M69" s="10" t="n"/>
-      <c r="N69" s="10" t="n"/>
-      <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="10" t="n"/>
-      <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
-      <c r="T69" s="10" t="n"/>
-      <c r="U69" s="10" t="n"/>
-      <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n"/>
-      <c r="X69" s="10" t="n"/>
-      <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="10" t="n"/>
-      <c r="AA69" s="10" t="n"/>
-      <c r="AB69" s="10" t="n"/>
-      <c r="AC69" s="10" t="n"/>
-      <c r="AD69" s="10" t="n"/>
-      <c r="AE69" s="10" t="n"/>
-      <c r="AF69" s="10" t="n"/>
-      <c r="AG69" s="10" t="n"/>
-      <c r="AH69" s="10" t="n"/>
-      <c r="AI69" s="10" t="n"/>
-      <c r="AJ69" s="10" t="n"/>
-      <c r="AK69" s="11" t="n"/>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="27" t="inlineStr">
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="10" t="n"/>
+      <c r="Q65" s="10" t="n"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="10" t="n"/>
+      <c r="X65" s="10" t="n"/>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="10" t="n"/>
+      <c r="AE65" s="10" t="n"/>
+      <c r="AF65" s="10" t="n"/>
+      <c r="AG65" s="10" t="n"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="10" t="n"/>
+      <c r="AJ65" s="10" t="n"/>
+      <c r="AK65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="B66" s="27" t="inlineStr">
         <is>
           <t>4.5 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
+    <row r="67" ht="18" customHeight="1">
+      <c r="C67" s="41" t="inlineStr">
         <is>
           <t>件数を含む data オブジェクトを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="27" t="inlineStr">
+    <row r="68" ht="18" customHeight="1">
+      <c r="B68" s="27" t="inlineStr">
         <is>
           <t>4.6 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="C73" s="41" t="inlineStr">
+    <row r="69" ht="18" customHeight="1">
+      <c r="C69" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="109">
+  <mergeCells count="106">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y27:AE27"/>
-    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C53:AK53"/>
     <mergeCell ref="C34:AK34"/>
+    <mergeCell ref="D58:AK58"/>
     <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
-    <mergeCell ref="D64:AK64"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="B49:AK49"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="A49:AK49"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Y21:AB21"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="C31:AK31"/>
     <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="C51:AK51"/>
-    <mergeCell ref="B50:AK50"/>
     <mergeCell ref="Y26:AE26"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
+    <mergeCell ref="C48:AK48"/>
     <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B66:AK66"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="A23:AK23"/>
+    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D56:AK56"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="Z2:AC3"/>
@@ -7613,59 +7371,58 @@
     <mergeCell ref="C55:AK55"/>
     <mergeCell ref="D63:AK63"/>
     <mergeCell ref="C26:L26"/>
+    <mergeCell ref="B64:AK64"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="B33:I33"/>
+    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M21:P21"/>
     <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="D66:AK66"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="C37:AK37"/>
     <mergeCell ref="D27:L27"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="B52:AK52"/>
     <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="B60:AK60"/>
-    <mergeCell ref="C62:AK62"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="D28:L28"/>
-    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="C54:AK54"/>
     <mergeCell ref="T21:X21"/>
+    <mergeCell ref="C50:AK50"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="C43:AK43"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="D57:AK57"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="Y25:AE25"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="B72:AK72"/>
+    <mergeCell ref="B54:AK54"/>
     <mergeCell ref="B14:I17"/>
+    <mergeCell ref="C67:AK67"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
-    <mergeCell ref="B70:AK70"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="C69:AK69"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="A19:AK19"/>
     <mergeCell ref="B42:I42"/>
-    <mergeCell ref="D67:AK67"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="D59:AK59"/>
+    <mergeCell ref="D60:AK60"/>
     <mergeCell ref="B68:AK68"/>
     <mergeCell ref="C40:AK40"/>
     <mergeCell ref="AF28:AK28"/>
@@ -7673,8 +7430,9 @@
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C21:L21"/>
+    <mergeCell ref="A46:AK46"/>
+    <mergeCell ref="B47:AK47"/>
     <mergeCell ref="M28:P28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
